--- a/宾客链接.xlsx
+++ b/宾客链接.xlsx
@@ -536,7 +536,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>张三</t>
+          <t>苏捷</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -551,7 +551,7 @@
       </c>
       <c r="E2" s="5" t="inlineStr">
         <is>
-          <t>https://summertweet.github.io/wedding-invitation/?name=%E5%BC%A0%E4%B8%89</t>
+          <t>https://summertweet.github.io/wedding-invitation/?name=%E8%8B%8F%E6%8D%B7</t>
         </is>
       </c>
     </row>
@@ -561,7 +561,7 @@
       </c>
       <c r="B3" s="7" t="inlineStr">
         <is>
-          <t>李四</t>
+          <t>庄文曦</t>
         </is>
       </c>
       <c r="C3" s="6" t="inlineStr">
@@ -576,7 +576,7 @@
       </c>
       <c r="E3" s="9" t="inlineStr">
         <is>
-          <t>https://summertweet.github.io/wedding-invitation/?name=%E6%9D%8E%E5%9B%9B</t>
+          <t>https://summertweet.github.io/wedding-invitation/?name=%E5%BA%84%E6%96%87%E6%9B%A6</t>
         </is>
       </c>
     </row>
@@ -586,7 +586,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>王五</t>
+          <t>刘筱</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -601,7 +601,7 @@
       </c>
       <c r="E4" s="5" t="inlineStr">
         <is>
-          <t>https://summertweet.github.io/wedding-invitation/?name=%E7%8E%8B%E4%BA%94</t>
+          <t>https://summertweet.github.io/wedding-invitation/?name=%E5%88%98%E7%AD%B1</t>
         </is>
       </c>
     </row>
@@ -611,7 +611,7 @@
       </c>
       <c r="B5" s="7" t="inlineStr">
         <is>
-          <t>赵六</t>
+          <t>黄志煌</t>
         </is>
       </c>
       <c r="C5" s="6" t="inlineStr">
@@ -626,7 +626,7 @@
       </c>
       <c r="E5" s="9" t="inlineStr">
         <is>
-          <t>https://summertweet.github.io/wedding-invitation/?name=%E8%B5%B5%E5%85%AD</t>
+          <t>https://summertweet.github.io/wedding-invitation/?name=%E9%BB%84%E5%BF%97%E7%85%8C</t>
         </is>
       </c>
     </row>
